--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -494,12 +494,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>test</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>adopt</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">

--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -464,12 +464,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Techniques</t>
+          <t>techniques</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Adopt</t>
+          <t>wow!</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>test</t>
+          <t>test 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">

--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,11 +447,27 @@
           <t>status</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>linkName</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This is a sample entry. Edit or delete it.&lt;/p&gt;</t>
+          <t>&lt;p&gt;This is a sample entry. Edit or delete it.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;pre&gt;jjiij 
+&lt;/pre&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;a href="mailto:sucess" target="_blank" rel="noopener noreferrer"&gt;ijjij&lt;/a&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;ok&lt;/li&gt;&lt;/ul&gt;&lt;ol&gt;&lt;li&gt;okok&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
       <c r="B2" t="b">
@@ -475,13 +491,24 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>new</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Yey</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>mailto:success</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>hello</t>
+          <t>&lt;p&gt;hello&lt;/p&gt;</t>
         </is>
       </c>
       <c r="B3" t="b">
@@ -494,7 +521,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>test 1</t>
+          <t>test-1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -505,6 +532,17 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>ok</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>link name!</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>mailto:link</t>
         </is>
       </c>
     </row>

--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -413,136 +413,48 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ring</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>quadrant</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>isNew</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>quadrant</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ring</t>
-        </is>
-      </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>tags</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>tags</t>
+          <t>link</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>linkName</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>link</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;This is a sample entry. Edit or delete it.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;pre&gt;jjiij 
-&lt;/pre&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;a href="mailto:sucess" target="_blank" rel="noopener noreferrer"&gt;ijjij&lt;/a&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;ok&lt;/li&gt;&lt;/ul&gt;&lt;ol&gt;&lt;li&gt;okok&lt;/li&gt;&lt;/ol&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="B2" t="b">
-        <v>0</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Sample Entry</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>techniques</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>wow!</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>new</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Yey</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>mailto:success</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;hello&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="B3" t="b">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>test-1</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>adopt</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>link name!</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>mailto:link</t>
         </is>
       </c>
     </row>
